--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/43.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/43.xlsx
@@ -426,13 +426,13 @@
         <v>-6.739360359643106</v>
       </c>
       <c r="E2">
-        <v>-16.09231032630685</v>
+        <v>-19.61931230718091</v>
       </c>
       <c r="F2">
-        <v>-4.146788313211569</v>
+        <v>-4.664191563204557</v>
       </c>
       <c r="G2">
-        <v>-14.48262651331753</v>
+        <v>-14.15721809480764</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.499276625132824</v>
       </c>
       <c r="E3">
-        <v>-16.69713784324532</v>
+        <v>-19.82224228441263</v>
       </c>
       <c r="F3">
-        <v>-4.295952431433675</v>
+        <v>-4.554826356849952</v>
       </c>
       <c r="G3">
-        <v>-12.04858928738763</v>
+        <v>-14.01169975508343</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.290357392589339</v>
       </c>
       <c r="E4">
-        <v>-14.75986119123794</v>
+        <v>-19.97579378106472</v>
       </c>
       <c r="F4">
-        <v>-4.233732099074599</v>
+        <v>-4.29332899186901</v>
       </c>
       <c r="G4">
-        <v>-13.12269247705863</v>
+        <v>-13.90132616680413</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.121459102984435</v>
       </c>
       <c r="E5">
-        <v>-16.77418982848583</v>
+        <v>-20.98298979900672</v>
       </c>
       <c r="F5">
-        <v>-4.212378444165234</v>
+        <v>-4.354054949433436</v>
       </c>
       <c r="G5">
-        <v>-12.86338737660413</v>
+        <v>-13.71885055195227</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.986954562079109</v>
       </c>
       <c r="E6">
-        <v>-17.22840935687719</v>
+        <v>-21.05516914621498</v>
       </c>
       <c r="F6">
-        <v>-4.541144212457913</v>
+        <v>-4.463684404989533</v>
       </c>
       <c r="G6">
-        <v>-13.13431911299255</v>
+        <v>-13.67773192108176</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.881492977064856</v>
       </c>
       <c r="E7">
-        <v>-17.60226658552843</v>
+        <v>-21.11225508955567</v>
       </c>
       <c r="F7">
-        <v>-4.088838214813923</v>
+        <v>-4.486964014110407</v>
       </c>
       <c r="G7">
-        <v>-12.61629818918955</v>
+        <v>-13.59907004852313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.793504058055271</v>
       </c>
       <c r="E8">
-        <v>-18.16834847885726</v>
+        <v>-22.71496808187635</v>
       </c>
       <c r="F8">
-        <v>-4.584491021911605</v>
+        <v>-4.420268841041408</v>
       </c>
       <c r="G8">
-        <v>-13.31633290674168</v>
+        <v>-13.7052591072408</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.708601872856227</v>
       </c>
       <c r="E9">
-        <v>-18.62216950153595</v>
+        <v>-22.34494647070961</v>
       </c>
       <c r="F9">
-        <v>-3.830958330281006</v>
+        <v>-4.32523273402043</v>
       </c>
       <c r="G9">
-        <v>-11.80446634877623</v>
+        <v>-13.1614093071404</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.623014442481802</v>
       </c>
       <c r="E10">
-        <v>-20.25347075026705</v>
+        <v>-22.82710668372829</v>
       </c>
       <c r="F10">
-        <v>-3.939193643498193</v>
+        <v>-4.012606047836494</v>
       </c>
       <c r="G10">
-        <v>-11.0895772133894</v>
+        <v>-13.65750779838235</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.530322368597295</v>
       </c>
       <c r="E11">
-        <v>-19.87929199996127</v>
+        <v>-23.6230675031085</v>
       </c>
       <c r="F11">
-        <v>-4.419563072014223</v>
+        <v>-4.050835203475691</v>
       </c>
       <c r="G11">
-        <v>-10.5738240132808</v>
+        <v>-12.57388347974041</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.424901225726625</v>
       </c>
       <c r="E12">
-        <v>-19.42091986090487</v>
+        <v>-25.00625818943335</v>
       </c>
       <c r="F12">
-        <v>-3.711255927106867</v>
+        <v>-3.846580511130402</v>
       </c>
       <c r="G12">
-        <v>-10.7301744580095</v>
+        <v>-12.71565097136862</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.299042363667174</v>
       </c>
       <c r="E13">
-        <v>-19.42758124617016</v>
+        <v>-24.61658300107332</v>
       </c>
       <c r="F13">
-        <v>-3.475448720388945</v>
+        <v>-3.849910548089656</v>
       </c>
       <c r="G13">
-        <v>-11.33464034693394</v>
+        <v>-12.20842904711472</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.158121072079281</v>
       </c>
       <c r="E14">
-        <v>-20.70278594130811</v>
+        <v>-25.55294462858733</v>
       </c>
       <c r="F14">
-        <v>-3.601278557241593</v>
+        <v>-3.997258884964827</v>
       </c>
       <c r="G14">
-        <v>-11.22051591055865</v>
+        <v>-12.00953809220639</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.004399407775675</v>
       </c>
       <c r="E15">
-        <v>-22.7119249473432</v>
+        <v>-26.0619541639975</v>
       </c>
       <c r="F15">
-        <v>-2.600046616458484</v>
+        <v>-3.440566997424461</v>
       </c>
       <c r="G15">
-        <v>-11.12795967837171</v>
+        <v>-11.3977095500026</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.841918987688278</v>
       </c>
       <c r="E16">
-        <v>-23.55235990995273</v>
+        <v>-26.20586906796126</v>
       </c>
       <c r="F16">
-        <v>-2.983321444957579</v>
+        <v>-3.417322179734504</v>
       </c>
       <c r="G16">
-        <v>-10.96637526114542</v>
+        <v>-11.20391683522474</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.672544351333655</v>
       </c>
       <c r="E17">
-        <v>-24.23056229123748</v>
+        <v>-27.61340483055136</v>
       </c>
       <c r="F17">
-        <v>-2.74492890357552</v>
+        <v>-3.218034378336402</v>
       </c>
       <c r="G17">
-        <v>-10.60119891434503</v>
+        <v>-10.76636865239035</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.509187579650711</v>
       </c>
       <c r="E18">
-        <v>-23.4725183847235</v>
+        <v>-27.08904376825519</v>
       </c>
       <c r="F18">
-        <v>-2.5291541057595</v>
+        <v>-3.089837067446553</v>
       </c>
       <c r="G18">
-        <v>-10.35408655311167</v>
+        <v>-10.68900782422866</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.36043603028513</v>
       </c>
       <c r="E19">
-        <v>-25.49237628873474</v>
+        <v>-28.77660224958359</v>
       </c>
       <c r="F19">
-        <v>-2.501889221063756</v>
+        <v>-2.882356712434764</v>
       </c>
       <c r="G19">
-        <v>-9.436532440901733</v>
+        <v>-9.937017404983211</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.232224743702551</v>
       </c>
       <c r="E20">
-        <v>-26.41297882670207</v>
+        <v>-28.9066736085059</v>
       </c>
       <c r="F20">
-        <v>-2.189126682625761</v>
+        <v>-2.843618939210248</v>
       </c>
       <c r="G20">
-        <v>-9.432933877900544</v>
+        <v>-10.5917042697384</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.12346212131285</v>
       </c>
       <c r="E21">
-        <v>-26.35803032309299</v>
+        <v>-29.28027724261272</v>
       </c>
       <c r="F21">
-        <v>-2.002744845363275</v>
+        <v>-2.501977856375856</v>
       </c>
       <c r="G21">
-        <v>-9.063970267003231</v>
+        <v>-9.856048082183715</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.038294127962097</v>
       </c>
       <c r="E22">
-        <v>-25.37075053383673</v>
+        <v>-30.24747551388196</v>
       </c>
       <c r="F22">
-        <v>-2.236927623604307</v>
+        <v>-2.522610831644786</v>
       </c>
       <c r="G22">
-        <v>-9.637326959495148</v>
+        <v>-9.925847624333709</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.974814579067504</v>
       </c>
       <c r="E23">
-        <v>-28.15688963858191</v>
+        <v>-31.34196918950682</v>
       </c>
       <c r="F23">
-        <v>-1.703563390494178</v>
+        <v>-2.194576511768779</v>
       </c>
       <c r="G23">
-        <v>-8.900631260641131</v>
+        <v>-9.958072474612976</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.927890874066012</v>
       </c>
       <c r="E24">
-        <v>-27.07448925279454</v>
+        <v>-30.99854783466113</v>
       </c>
       <c r="F24">
-        <v>-1.270726511918186</v>
+        <v>-2.205597940063027</v>
       </c>
       <c r="G24">
-        <v>-8.617476990121727</v>
+        <v>-9.469071793007229</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.887657817271525</v>
       </c>
       <c r="E25">
-        <v>-28.35301331938011</v>
+        <v>-31.11128193084508</v>
       </c>
       <c r="F25">
-        <v>-1.292832324429293</v>
+        <v>-2.029206213678303</v>
       </c>
       <c r="G25">
-        <v>-8.82241631173031</v>
+        <v>-9.807555211124471</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.851291675512023</v>
       </c>
       <c r="E26">
-        <v>-27.68376825968254</v>
+        <v>-31.36036385092598</v>
       </c>
       <c r="F26">
-        <v>-1.556374928527748</v>
+        <v>-2.190125693713537</v>
       </c>
       <c r="G26">
-        <v>-9.168441152586013</v>
+        <v>-9.823469003531748</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.813983532434279</v>
       </c>
       <c r="E27">
-        <v>-28.16441596238266</v>
+        <v>-31.89482567449625</v>
       </c>
       <c r="F27">
-        <v>-1.123532251379936</v>
+        <v>-2.1666497615182</v>
       </c>
       <c r="G27">
-        <v>-8.42395242953255</v>
+        <v>-9.365153768529506</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.771015231034724</v>
       </c>
       <c r="E28">
-        <v>-27.8306945988614</v>
+        <v>-31.33957589099377</v>
       </c>
       <c r="F28">
-        <v>-1.312553267187741</v>
+        <v>-1.817353735514537</v>
       </c>
       <c r="G28">
-        <v>-8.099826847419127</v>
+        <v>-9.818340968491418</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.716183282635076</v>
       </c>
       <c r="E29">
-        <v>-29.41025350358087</v>
+        <v>-31.79754273162647</v>
       </c>
       <c r="F29">
-        <v>-0.9061114875345526</v>
+        <v>-1.885942556466337</v>
       </c>
       <c r="G29">
-        <v>-9.288673545481263</v>
+        <v>-9.754053484664309</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.650881422553509</v>
       </c>
       <c r="E30">
-        <v>-27.54127076808317</v>
+        <v>-31.57195000622336</v>
       </c>
       <c r="F30">
-        <v>-1.241977192836626</v>
+        <v>-2.201549708565545</v>
       </c>
       <c r="G30">
-        <v>-8.45475374522993</v>
+        <v>-9.558098983649309</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.576374813523727</v>
       </c>
       <c r="E31">
-        <v>-28.32452468939785</v>
+        <v>-31.47477801096677</v>
       </c>
       <c r="F31">
-        <v>-2.252413952199643</v>
+        <v>-1.715056988208021</v>
       </c>
       <c r="G31">
-        <v>-8.457620677666938</v>
+        <v>-9.736937964226279</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.493933020911088</v>
       </c>
       <c r="E32">
-        <v>-27.55809857749568</v>
+        <v>-30.49931074615952</v>
       </c>
       <c r="F32">
-        <v>-1.333475342680248</v>
+        <v>-1.920166555712998</v>
       </c>
       <c r="G32">
-        <v>-8.255558220131983</v>
+        <v>-9.28636940578593</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.402636517864291</v>
       </c>
       <c r="E33">
-        <v>-29.05356824836671</v>
+        <v>-31.06521150052805</v>
       </c>
       <c r="F33">
-        <v>-1.217638930174974</v>
+        <v>-2.178199688215433</v>
       </c>
       <c r="G33">
-        <v>-8.069800199377937</v>
+        <v>-9.45884220729088</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.306806301938813</v>
       </c>
       <c r="E34">
-        <v>-26.61796473113327</v>
+        <v>-30.20390932969117</v>
       </c>
       <c r="F34">
-        <v>-1.33293441876622</v>
+        <v>-2.073724334639554</v>
       </c>
       <c r="G34">
-        <v>-8.447920779236874</v>
+        <v>-9.900459050593039</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.209421885341806</v>
       </c>
       <c r="E35">
-        <v>-27.11780410667791</v>
+        <v>-30.55123875760548</v>
       </c>
       <c r="F35">
-        <v>-1.333754502494992</v>
+        <v>-2.133913510126966</v>
       </c>
       <c r="G35">
-        <v>-7.627925133523715</v>
+        <v>-9.941758106195447</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.111432276322494</v>
       </c>
       <c r="E36">
-        <v>-26.06975219623871</v>
+        <v>-29.47223699156086</v>
       </c>
       <c r="F36">
-        <v>-1.176823611504237</v>
+        <v>-2.053357265306922</v>
       </c>
       <c r="G36">
-        <v>-8.90440197201036</v>
+        <v>-9.883264077062064</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.010891535410466</v>
       </c>
       <c r="E37">
-        <v>-25.96477311179289</v>
+        <v>-28.98144324284655</v>
       </c>
       <c r="F37">
-        <v>-1.335021904621275</v>
+        <v>-2.30809515228102</v>
       </c>
       <c r="G37">
-        <v>-8.012650251733499</v>
+        <v>-9.630772079327389</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.909451868022809</v>
       </c>
       <c r="E38">
-        <v>-25.02690350243432</v>
+        <v>-29.17941906951388</v>
       </c>
       <c r="F38">
-        <v>-1.55303495115966</v>
+        <v>-2.530904446081615</v>
       </c>
       <c r="G38">
-        <v>-8.584580099097987</v>
+        <v>-10.02186999770027</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.808008021648909</v>
       </c>
       <c r="E39">
-        <v>-25.14578953055769</v>
+        <v>-28.25232722829357</v>
       </c>
       <c r="F39">
-        <v>-1.260161514062881</v>
+        <v>-2.414031745955438</v>
       </c>
       <c r="G39">
-        <v>-7.941811198284173</v>
+        <v>-9.304491332067901</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.706034840751731</v>
       </c>
       <c r="E40">
-        <v>-24.38121556452465</v>
+        <v>-28.27302235450862</v>
       </c>
       <c r="F40">
-        <v>-1.517766380618068</v>
+        <v>-2.197217347048904</v>
       </c>
       <c r="G40">
-        <v>-7.85370102875647</v>
+        <v>-9.320007859010465</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.601099990080175</v>
       </c>
       <c r="E41">
-        <v>-23.62741030968185</v>
+        <v>-27.70834881659617</v>
       </c>
       <c r="F41">
-        <v>-1.767382471940657</v>
+        <v>-2.194187179089464</v>
       </c>
       <c r="G41">
-        <v>-7.737762413425655</v>
+        <v>-9.596925061733881</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.494490300942558</v>
       </c>
       <c r="E42">
-        <v>-23.42392333014719</v>
+        <v>-27.18620670656377</v>
       </c>
       <c r="F42">
-        <v>-1.606353647408253</v>
+        <v>-2.358205581578571</v>
       </c>
       <c r="G42">
-        <v>-8.889603833449817</v>
+        <v>-10.23752555521947</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.387542216955852</v>
       </c>
       <c r="E43">
-        <v>-22.68488995751741</v>
+        <v>-26.75807571693059</v>
       </c>
       <c r="F43">
-        <v>-2.247851304545024</v>
+        <v>-2.231813283259422</v>
       </c>
       <c r="G43">
-        <v>-8.443024482384292</v>
+        <v>-9.075547244754063</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.281003614432179</v>
       </c>
       <c r="E44">
-        <v>-23.09731167081797</v>
+        <v>-25.92167109618789</v>
       </c>
       <c r="F44">
-        <v>-1.990912445381687</v>
+        <v>-2.510621870224069</v>
       </c>
       <c r="G44">
-        <v>-8.240849466301</v>
+        <v>-9.729773943679294</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.174724789605794</v>
       </c>
       <c r="E45">
-        <v>-21.17894592626663</v>
+        <v>-26.27216139895955</v>
       </c>
       <c r="F45">
-        <v>-1.767320344385447</v>
+        <v>-2.189094376297052</v>
       </c>
       <c r="G45">
-        <v>-8.255723747408945</v>
+        <v>-9.548942014687684</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.071992377120598</v>
       </c>
       <c r="E46">
-        <v>-21.63113669830255</v>
+        <v>-25.04805147605014</v>
       </c>
       <c r="F46">
-        <v>-1.724633743751786</v>
+        <v>-2.51705497147421</v>
       </c>
       <c r="G46">
-        <v>-8.966021156132815</v>
+        <v>-9.349047964480951</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.976234382880362</v>
       </c>
       <c r="E47">
-        <v>-21.64772902706666</v>
+        <v>-24.72678794452398</v>
       </c>
       <c r="F47">
-        <v>-1.605520309801037</v>
+        <v>-2.204488756110678</v>
       </c>
       <c r="G47">
-        <v>-8.777475656034703</v>
+        <v>-9.814782132036701</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.889389819544321</v>
       </c>
       <c r="E48">
-        <v>-20.15402546105861</v>
+        <v>-24.24884374080644</v>
       </c>
       <c r="F48">
-        <v>-1.81253429396505</v>
+        <v>-2.511678038662638</v>
       </c>
       <c r="G48">
-        <v>-8.822525559733105</v>
+        <v>-9.230093442163859</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.811599413032421</v>
       </c>
       <c r="E49">
-        <v>-20.27674710666648</v>
+        <v>-23.12909702987781</v>
       </c>
       <c r="F49">
-        <v>-1.639456865558927</v>
+        <v>-2.409955349966262</v>
       </c>
       <c r="G49">
-        <v>-9.184447640268388</v>
+        <v>-9.400351488703038</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.745107623993218</v>
       </c>
       <c r="E50">
-        <v>-19.37733329858105</v>
+        <v>-23.56896129566485</v>
       </c>
       <c r="F50">
-        <v>-2.043551051992582</v>
+        <v>-2.528643831439375</v>
       </c>
       <c r="G50">
-        <v>-8.269498927397853</v>
+        <v>-9.723828203890765</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.693497251064287</v>
       </c>
       <c r="E51">
-        <v>-20.0368285537401</v>
+        <v>-22.91406697009759</v>
       </c>
       <c r="F51">
-        <v>-2.250810232907824</v>
+        <v>-2.604662279626883</v>
       </c>
       <c r="G51">
-        <v>-7.383726052364915</v>
+        <v>-9.619887005594267</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.65958360739689</v>
       </c>
       <c r="E52">
-        <v>-18.62943770231826</v>
+        <v>-22.74849237495514</v>
       </c>
       <c r="F52">
-        <v>-2.232023688579734</v>
+        <v>-2.778973975463177</v>
       </c>
       <c r="G52">
-        <v>-7.770020369160313</v>
+        <v>-10.00553245546397</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.644713190611848</v>
       </c>
       <c r="E53">
-        <v>-19.10090618820483</v>
+        <v>-22.28129424005779</v>
       </c>
       <c r="F53">
-        <v>-1.902739362292902</v>
+        <v>-2.408496594969932</v>
       </c>
       <c r="G53">
-        <v>-7.914896463049899</v>
+        <v>-10.13262429871659</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.651568154726807</v>
       </c>
       <c r="E54">
-        <v>-17.88064999667596</v>
+        <v>-21.76956309176902</v>
       </c>
       <c r="F54">
-        <v>-2.274924008003317</v>
+        <v>-2.579803802236273</v>
       </c>
       <c r="G54">
-        <v>-8.19696818517796</v>
+        <v>-10.54702845768594</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.684192010798939</v>
       </c>
       <c r="E55">
-        <v>-18.77563495718189</v>
+        <v>-21.84877063063718</v>
       </c>
       <c r="F55">
-        <v>-1.666360582067049</v>
+        <v>-2.541839724165971</v>
       </c>
       <c r="G55">
-        <v>-7.791641542077293</v>
+        <v>-10.224882581805</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.744753763003865</v>
       </c>
       <c r="E56">
-        <v>-18.01071682712426</v>
+        <v>-21.44478999288692</v>
       </c>
       <c r="F56">
-        <v>-2.644287234339797</v>
+        <v>-2.324220980511319</v>
       </c>
       <c r="G56">
-        <v>-8.599027319831368</v>
+        <v>-10.59165792210085</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.832756329109904</v>
       </c>
       <c r="E57">
-        <v>-16.26663846170613</v>
+        <v>-21.35118190667436</v>
       </c>
       <c r="F57">
-        <v>-2.233944672586825</v>
+        <v>-2.358627220586596</v>
       </c>
       <c r="G57">
-        <v>-8.268105187725819</v>
+        <v>-10.26811499600234</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.94693241090467</v>
       </c>
       <c r="E58">
-        <v>-17.23914184027537</v>
+        <v>-19.9365228544702</v>
       </c>
       <c r="F58">
-        <v>-1.885971549325435</v>
+        <v>-2.660041953973641</v>
       </c>
       <c r="G58">
-        <v>-9.14901156081603</v>
+        <v>-10.72492724332975</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.087222128736121</v>
       </c>
       <c r="E59">
-        <v>-17.43074610401391</v>
+        <v>-20.43523463998693</v>
       </c>
       <c r="F59">
-        <v>-2.456411850650064</v>
+        <v>-2.616617277984085</v>
       </c>
       <c r="G59">
-        <v>-8.353030612444744</v>
+        <v>-10.55240809418725</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.250546518252563</v>
       </c>
       <c r="E60">
-        <v>-15.4851234744104</v>
+        <v>-19.80598053425109</v>
       </c>
       <c r="F60">
-        <v>-2.380600494313256</v>
+        <v>-2.572230867439879</v>
       </c>
       <c r="G60">
-        <v>-8.11116546589113</v>
+        <v>-10.91038069389419</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.431261291512287</v>
       </c>
       <c r="E61">
-        <v>-15.96955245290693</v>
+        <v>-19.51505777857632</v>
       </c>
       <c r="F61">
-        <v>-2.473115050960113</v>
+        <v>-2.568965443138044</v>
       </c>
       <c r="G61">
-        <v>-8.47573267231229</v>
+        <v>-10.18599691390072</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.622895399707411</v>
       </c>
       <c r="E62">
-        <v>-17.40256993873818</v>
+        <v>-19.70035387802218</v>
       </c>
       <c r="F62">
-        <v>-2.457352876019644</v>
+        <v>-2.580457384117081</v>
       </c>
       <c r="G62">
-        <v>-8.494387596426083</v>
+        <v>-10.96232646395089</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.821717584832441</v>
       </c>
       <c r="E63">
-        <v>-15.85191628360967</v>
+        <v>-19.84016598453499</v>
       </c>
       <c r="F63">
-        <v>-2.309046118059435</v>
+        <v>-2.959010518420219</v>
       </c>
       <c r="G63">
-        <v>-8.66315589747259</v>
+        <v>-10.30795079047639</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.021642182056265</v>
       </c>
       <c r="E64">
-        <v>-15.84704817405143</v>
+        <v>-18.73808937918429</v>
       </c>
       <c r="F64">
-        <v>-2.088412945425995</v>
+        <v>-2.476063210546676</v>
       </c>
       <c r="G64">
-        <v>-8.601977015906858</v>
+        <v>-10.46441379375342</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.215159028240055</v>
       </c>
       <c r="E65">
-        <v>-15.89403562035501</v>
+        <v>-19.2380917797932</v>
       </c>
       <c r="F65">
-        <v>-2.233433569899298</v>
+        <v>-2.862491633748229</v>
       </c>
       <c r="G65">
-        <v>-8.845434534864861</v>
+        <v>-11.15296753937536</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.394818629511424</v>
       </c>
       <c r="E66">
-        <v>-15.90505792608968</v>
+        <v>-19.19893406504887</v>
       </c>
       <c r="F66">
-        <v>-2.74207931970989</v>
+        <v>-2.816970359862188</v>
       </c>
       <c r="G66">
-        <v>-8.488316055907061</v>
+        <v>-11.15283842809933</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.557779412998519</v>
       </c>
       <c r="E67">
-        <v>-15.65658508576282</v>
+        <v>-19.76669149376054</v>
       </c>
       <c r="F67">
-        <v>-2.634028732423528</v>
+        <v>-2.977415185375619</v>
       </c>
       <c r="G67">
-        <v>-8.620843814935165</v>
+        <v>-10.97353266060132</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.700153879370351</v>
       </c>
       <c r="E68">
-        <v>-15.9623340653387</v>
+        <v>-18.93582972520322</v>
       </c>
       <c r="F68">
-        <v>-2.801768989653414</v>
+        <v>-2.676472621408169</v>
       </c>
       <c r="G68">
-        <v>-8.546442614485585</v>
+        <v>-10.73648766835289</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.817706330176336</v>
       </c>
       <c r="E69">
-        <v>-15.73368688421741</v>
+        <v>-19.87096866473517</v>
       </c>
       <c r="F69">
-        <v>-2.042217380474074</v>
+        <v>-2.872840427711403</v>
       </c>
       <c r="G69">
-        <v>-8.328698102731101</v>
+        <v>-10.73799065602772</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.906707899948302</v>
       </c>
       <c r="E70">
-        <v>-15.85968714500684</v>
+        <v>-18.93534970695841</v>
       </c>
       <c r="F70">
-        <v>-2.782142480778885</v>
+        <v>-2.932313065395394</v>
       </c>
       <c r="G70">
-        <v>-8.378343043638012</v>
+        <v>-10.33609704865127</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.967749904992738</v>
       </c>
       <c r="E71">
-        <v>-15.32728804134705</v>
+        <v>-18.71666064018</v>
       </c>
       <c r="F71">
-        <v>-2.607692447586323</v>
+        <v>-2.78642265514915</v>
       </c>
       <c r="G71">
-        <v>-7.636549104653517</v>
+        <v>-10.29642347090865</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.99928838212584</v>
       </c>
       <c r="E72">
-        <v>-15.51454044156422</v>
+        <v>-20.2556851740568</v>
       </c>
       <c r="F72">
-        <v>-2.826351620698892</v>
+        <v>-3.157592550791136</v>
       </c>
       <c r="G72">
-        <v>-9.221823699406761</v>
+        <v>-10.54263536375533</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.998261790761418</v>
       </c>
       <c r="E73">
-        <v>-16.38241342818623</v>
+        <v>-20.00383862059422</v>
       </c>
       <c r="F73">
-        <v>-2.867576981234015</v>
+        <v>-3.140640840260247</v>
       </c>
       <c r="G73">
-        <v>-8.485276975102011</v>
+        <v>-10.65415440079121</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.961333395200267</v>
       </c>
       <c r="E74">
-        <v>-17.64918157624789</v>
+        <v>-19.32788236241728</v>
       </c>
       <c r="F74">
-        <v>-3.0725407560761</v>
+        <v>-3.300143812036695</v>
       </c>
       <c r="G74">
-        <v>-8.023277102914559</v>
+        <v>-10.20821067446923</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.888091707351162</v>
       </c>
       <c r="E75">
-        <v>-15.5168273209381</v>
+        <v>-18.83141217153436</v>
       </c>
       <c r="F75">
-        <v>-2.551782618101774</v>
+        <v>-3.22159635816844</v>
       </c>
       <c r="G75">
-        <v>-8.718577740345529</v>
+        <v>-10.47709318316883</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.776379269161772</v>
       </c>
       <c r="E76">
-        <v>-16.29776266356085</v>
+        <v>-19.93318084065254</v>
       </c>
       <c r="F76">
-        <v>-2.347919743538009</v>
+        <v>-3.17022266858162</v>
       </c>
       <c r="G76">
-        <v>-8.182368679349775</v>
+        <v>-10.08655474699209</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.62381521614653</v>
       </c>
       <c r="E77">
-        <v>-16.85603293922645</v>
+        <v>-20.4714080903602</v>
       </c>
       <c r="F77">
-        <v>-2.845194494010372</v>
+        <v>-3.304802550310039</v>
       </c>
       <c r="G77">
-        <v>-8.413153429983447</v>
+        <v>-10.18551357425198</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.430021100042743</v>
       </c>
       <c r="E78">
-        <v>-17.36118421478208</v>
+        <v>-20.96155653152841</v>
       </c>
       <c r="F78">
-        <v>-3.133397595690168</v>
+        <v>-3.69519553990139</v>
       </c>
       <c r="G78">
-        <v>-8.512635323438547</v>
+        <v>-9.986841115349241</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.198241883695586</v>
       </c>
       <c r="E79">
-        <v>-16.74397584990665</v>
+        <v>-20.71779783264353</v>
       </c>
       <c r="F79">
-        <v>-2.926949386462267</v>
+        <v>-3.360664334485227</v>
       </c>
       <c r="G79">
-        <v>-7.925092943310854</v>
+        <v>-9.729919607683023</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.931000859042035</v>
       </c>
       <c r="E80">
-        <v>-18.38901196030302</v>
+        <v>-20.95200597984624</v>
       </c>
       <c r="F80">
-        <v>-2.885683435924407</v>
+        <v>-3.334246869642548</v>
       </c>
       <c r="G80">
-        <v>-8.169563489203874</v>
+        <v>-9.041392346425402</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.631543030712755</v>
       </c>
       <c r="E81">
-        <v>-19.88079545333181</v>
+        <v>-22.02133718964748</v>
       </c>
       <c r="F81">
-        <v>-3.228866938862811</v>
+        <v>-3.755870967054245</v>
       </c>
       <c r="G81">
-        <v>-7.340626059989144</v>
+        <v>-9.356953547228731</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.305898969339438</v>
       </c>
       <c r="E82">
-        <v>-21.56355828068609</v>
+        <v>-23.15086993290669</v>
       </c>
       <c r="F82">
-        <v>-3.569744266951822</v>
+        <v>-3.683307639303814</v>
       </c>
       <c r="G82">
-        <v>-7.252813839559975</v>
+        <v>-9.128909928301574</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.964146067418882</v>
       </c>
       <c r="E83">
-        <v>-21.09947120743201</v>
+        <v>-23.16887967403519</v>
       </c>
       <c r="F83">
-        <v>-3.50106598232052</v>
+        <v>-3.724822100062514</v>
       </c>
       <c r="G83">
-        <v>-7.228385324025693</v>
+        <v>-9.188880460745473</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.616210564771497</v>
       </c>
       <c r="E84">
-        <v>-20.99901606851986</v>
+        <v>-24.7394314439534</v>
       </c>
       <c r="F84">
-        <v>-3.27171258603781</v>
+        <v>-3.81168470592007</v>
       </c>
       <c r="G84">
-        <v>-6.309189181228273</v>
+        <v>-8.973046133767149</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.272891418161036</v>
       </c>
       <c r="E85">
-        <v>-23.67347394728787</v>
+        <v>-24.95100174959176</v>
       </c>
       <c r="F85">
-        <v>-3.339651966945814</v>
+        <v>-3.846032960277152</v>
       </c>
       <c r="G85">
-        <v>-6.420337437163764</v>
+        <v>-8.795481713222799</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.9460116352921228</v>
       </c>
       <c r="E86">
-        <v>-22.47077012101273</v>
+        <v>-25.51117398434058</v>
       </c>
       <c r="F86">
-        <v>-3.708350842625249</v>
+        <v>-3.778436523473907</v>
       </c>
       <c r="G86">
-        <v>-7.633400775845669</v>
+        <v>-8.671865942786413</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6506521084621161</v>
       </c>
       <c r="E87">
-        <v>-24.05185059299877</v>
+        <v>-26.41348601579093</v>
       </c>
       <c r="F87">
-        <v>-3.873534758050095</v>
+        <v>-4.054127963901818</v>
       </c>
       <c r="G87">
-        <v>-6.801838084018297</v>
+        <v>-8.282449781547482</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3996164707610286</v>
       </c>
       <c r="E88">
-        <v>-25.13128935678513</v>
+        <v>-27.63493319598382</v>
       </c>
       <c r="F88">
-        <v>-3.590841956333722</v>
+        <v>-4.007447804019261</v>
       </c>
       <c r="G88">
-        <v>-6.523318577253873</v>
+        <v>-8.380941821886339</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.2049861668698349</v>
       </c>
       <c r="E89">
-        <v>-27.53826838981609</v>
+        <v>-29.04185761458288</v>
       </c>
       <c r="F89">
-        <v>-3.929814867763697</v>
+        <v>-4.001447110553381</v>
       </c>
       <c r="G89">
-        <v>-6.527039630440013</v>
+        <v>-8.130542088932485</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.07684221006263516</v>
       </c>
       <c r="E90">
-        <v>-28.2971545924955</v>
+        <v>-30.18246021255384</v>
       </c>
       <c r="F90">
-        <v>-3.852152938649035</v>
+        <v>-4.121141230053493</v>
       </c>
       <c r="G90">
-        <v>-7.296181986124428</v>
+        <v>-9.186563078867982</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.02980489983513803</v>
       </c>
       <c r="E91">
-        <v>-29.75905921402168</v>
+        <v>-31.45621806024634</v>
       </c>
       <c r="F91">
-        <v>-3.73934338063359</v>
+        <v>-4.368245711410794</v>
       </c>
       <c r="G91">
-        <v>-7.169533755974069</v>
+        <v>-8.225822900098247</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.07403451705683151</v>
       </c>
       <c r="E92">
-        <v>-31.24275258823577</v>
+        <v>-32.7092875744348</v>
       </c>
       <c r="F92">
-        <v>-3.866917759236533</v>
+        <v>-3.963759707195615</v>
       </c>
       <c r="G92">
-        <v>-7.547756962744724</v>
+        <v>-9.137467688520591</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.2165810136982154</v>
       </c>
       <c r="E93">
-        <v>-33.09625020686423</v>
+        <v>-34.25159072349316</v>
       </c>
       <c r="F93">
-        <v>-3.55841385761633</v>
+        <v>-4.277514629782164</v>
       </c>
       <c r="G93">
-        <v>-6.389728133107663</v>
+        <v>-8.766014547377745</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4567626564114343</v>
       </c>
       <c r="E94">
-        <v>-35.12605263979633</v>
+        <v>-36.46544166128199</v>
       </c>
       <c r="F94">
-        <v>-3.870888952565554</v>
+        <v>-4.484703399468168</v>
       </c>
       <c r="G94">
-        <v>-6.579488603418687</v>
+        <v>-9.067691320189372</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.7948900871196239</v>
       </c>
       <c r="E95">
-        <v>-36.10704237865593</v>
+        <v>-36.93779546383707</v>
       </c>
       <c r="F95">
-        <v>-3.110709440894893</v>
+        <v>-4.287132803696069</v>
       </c>
       <c r="G95">
-        <v>-7.045507477890814</v>
+        <v>-9.216695664366428</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.229197692147829</v>
       </c>
       <c r="E96">
-        <v>-38.49195642208451</v>
+        <v>-39.74045444176222</v>
       </c>
       <c r="F96">
-        <v>-4.212813337051703</v>
+        <v>-4.448224584151086</v>
       </c>
       <c r="G96">
-        <v>-6.925278395541102</v>
+        <v>-9.60365871136076</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.742615772876687</v>
       </c>
       <c r="E97">
-        <v>-39.54055854211564</v>
+        <v>-41.11126880862412</v>
       </c>
       <c r="F97">
-        <v>-3.691650955784811</v>
+        <v>-4.477332586318058</v>
       </c>
       <c r="G97">
-        <v>-7.383716120728297</v>
+        <v>-9.730637996065045</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.329648849559684</v>
       </c>
       <c r="E98">
-        <v>-41.58884167747303</v>
+        <v>-42.96424112426769</v>
       </c>
       <c r="F98">
-        <v>-3.364431749433159</v>
+        <v>-4.389626702444452</v>
       </c>
       <c r="G98">
-        <v>-6.987357745493515</v>
+        <v>-10.45556801607249</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.956583308574125</v>
       </c>
       <c r="E99">
-        <v>-44.32234632882707</v>
+        <v>-44.71615827819311</v>
       </c>
       <c r="F99">
-        <v>-4.276844480553299</v>
+        <v>-4.416721771822621</v>
       </c>
       <c r="G99">
-        <v>-7.975784016608174</v>
+        <v>-9.716905853168148</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.635068166104049</v>
       </c>
       <c r="E100">
-        <v>-45.40450670549203</v>
+        <v>-46.89811743778292</v>
       </c>
       <c r="F100">
-        <v>-4.050971884097152</v>
+        <v>-4.377431477540438</v>
       </c>
       <c r="G100">
-        <v>-8.743810718445854</v>
+        <v>-10.66543011889797</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.297877841778168</v>
       </c>
       <c r="E101">
-        <v>-48.38418826085104</v>
+        <v>-48.57928284593099</v>
       </c>
       <c r="F101">
-        <v>-3.86103138047224</v>
+        <v>-4.677109124483812</v>
       </c>
       <c r="G101">
-        <v>-8.674219740664833</v>
+        <v>-10.81008109569089</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.00358974785129</v>
       </c>
       <c r="E102">
-        <v>-49.31376510218306</v>
+        <v>-50.44407108237908</v>
       </c>
       <c r="F102">
-        <v>-3.676835604785742</v>
+        <v>-4.879688857940639</v>
       </c>
       <c r="G102">
-        <v>-8.652184749555445</v>
+        <v>-11.36793119287686</v>
       </c>
     </row>
   </sheetData>
